--- a/output/graficos_dimensiones/comunal_d_dep_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2021_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-28 01:25</t>
+    <t xml:space="preserve">2026-08-17 16:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2021_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 16:13</t>
+    <t xml:space="preserve">2026-08-17 21:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2021_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 21:35</t>
+    <t xml:space="preserve">2026-09-01 17:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2021_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-01 17:28</t>
+    <t xml:space="preserve">2026-09-06 21:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
